--- a/output/OR202603121104075460_alternate_purchases.xlsx
+++ b/output/OR202603121104075460_alternate_purchases.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,7 +27,17 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -39,11 +49,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F4858"/>
+        <fgColor rgb="001F3650"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -51,14 +61,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <top style="medium">
+        <color rgb="00538135"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00538135"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9C9C9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9C9C9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9C9C9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9C9C9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,80 +464,90 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Schein SKU</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Original Product (Schein)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Schein Unit Price</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Recommended Equivalent</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Confidence</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Equivalency Basis</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+          <t>Alternate Purchase Recommendations  ·  Ref: OR202603121104075460  ·  Generated: 2026-06-12 16:39  ·  Items here do NOT appear in the Price Match report</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Includes equivalency-table substitutions and all matching scraped prices not in the Price Match report  ·  EXACT = same product · CLOSE = compatible specs · POSSIBLE = needs review</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Original Schein Product and
+Schein Price</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Recommended Equivalent Product</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Recommended Supplier</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Price of the
+Equivalent</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Product URL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Equivalent Price</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Pack/Qty Condition</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Est. Total Savings</t>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Match Score</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Equivalency Basis and Confidence Level</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Estimated Savings vs.
+Schein Price</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/OR202603121104075460_alternate_purchases.xlsx
+++ b/output/OR202603121104075460_alternate_purchases.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,8 +41,13 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <color rgb="000563C1"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +57,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3650"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF3EA"/>
       </patternFill>
     </fill>
   </fills>
@@ -87,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -98,6 +120,54 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -464,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -480,7 +550,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Alternate Purchase Recommendations  ·  Ref: OR202603121104075460  ·  Generated: 2026-06-12 16:39  ·  Items here do NOT appear in the Price Match report</t>
+          <t>Alternate Purchase Recommendations  ·  Ref: OR202603121104075460  ·  Generated: 2026-06-13 16:46  ·  Items here do NOT appear in the Price Match report</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -543,11 +613,2185 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="64" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx
+SKU: 5701400  ·  Schein price: $17.61/unit</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Syringe 3cc Luer Lock w/o Needle 100/Bx</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Medex Supply</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>https://medexsupply.com/syringe-3cc-luer-lock-w-o-needle-100-bx/</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>EXACT (100%)</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Non-Sterile)
+EXACT — same product, different brand or channel; substitution is straightforward
+Web search (not in Price Match) · EXACT (100%) · Matching: brand, product name, form/spec, pack size · Exact match in product name, size, and pack quantity.</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="5" ht="64" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea
+SKU: 1459489  ·  Schein price: $120.37/unit</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Silhouette-2 Low Profile Nasal Masks Medium 12/Pk</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Crazy Dental Price Club</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>97</v>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>https://www.crazydentalprices.com/Silhouette-Low-Profile-Nasal-Mask-new-SIL2-MED-12</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (77%)</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Medium)
+CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
+Web search (not in Price Match) · APPROXIMATE (77%) · Matching: brand, form/spec, pack size · Not matching: product name · Different product name, but same product family</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>23.37</v>
+      </c>
+    </row>
+    <row r="6" ht="64" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea
+SKU: 1459489  ·  Schein price: $120.37/unit</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Porter SIL2-MED-12 Medium Silhouette Low Profile Nasal Mask 12 Pack</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Broward A&amp;C Medical Supply</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>118</v>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>https://www.medicalgassupplier.com/product/porter-sil-med-12-silhouette-mask-medium-12-pack/</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (77%)</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Medium)
+CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
+Web search (not in Price Match) · APPROXIMATE (77%) · Matching: brand, form/spec, pack size · Not matching: product name · Different product name, but same product family</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="7" ht="64" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea
+SKU: 7770371  ·  Schein price: $32.20/unit</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>3M ESPE Clin pro Pit Fissure Sealant Low Viscosity Light Cure 1.2mL Syringe</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Tri County Dental Supply</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>https://tricountydental.com/products/3m-espe-dental-clinpro-sealnt-light-curing-low-viscosity</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (77%)</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page 1 vs ordered ?)
+CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
+Web search (not in Price Match) · APPROXIMATE (77%) · Matching: brand, product name, form/spec · Not matching: pack size · disagreeing title and scraped_product_name, but same product family</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="8" ht="64" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea
+SKU: 7770371  ·  Schein price: $32.20/unit</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>3M Clinpro Sealant Refill</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Crazy Dental Price Club</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>29.77</v>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>https://www.crazydentalprices.com/Clinpro-Sealant-12627</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (79%)</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page 1 vs ordered ?)
+CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
+Web search (not in Price Match) · APPROXIMATE (79%) · Matching: brand, product name, form/spec · Not matching: pack size · same product, but includes additional items</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="9" ht="64" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>Purevac SC Evacuation Cleaner 5 Liter Ea
+SKU: 3120099  ·  Schein price: $144.39/unit</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Purevac SC Evacuation System Cleaner, Citrus scent - 5L, 169 uses</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Net32</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>170.37</v>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/purevac-sc-evacuation-system-cleaner-5-liter169-d-143563</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (62%)</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page 64 vs ordered ?) · VARIANT MISMATCH (ordered: specified)
+CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
+Web search (not in Price Match) · APPROXIMATE (62%) · Matching: brand, form/spec · Not matching: product name, pack size · Different scent (Citrus) and pack quantity</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>Equiv $170.37 &gt; Schein $144.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="64" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Benzo-Jel Topical Anesthetic Strawberry 1oz/Jr
+SKU: 5700360  ·  Schein price: $6.29/unit</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>House Brand Strawberry Flavored Topical Anesthetic Gel (Benzocaine 20%), 1 Oz</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>SurgiMac Dental Supply</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>https://surgimac.com/products/strawberry-flavored-topical-anesthetic-gel-benzocaine-20-1-oz</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (62%)</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Strawberry)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (62%) · Matching: form/spec, pack size · Not matching: brand, product name · Different brand and product name</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Benzo-Jel Topical Anesthetic Strawberry 1oz/Jr
+SKU: 5700360  ·  Schein price: $6.29/unit</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Candi-Caine Topical Anesthetic Gel 1oz Strawberry</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Crazy Dental Price Club</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>https://www.crazydentalprices.com/Topical-Anesthetic-Gel-AN304_2</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (62%)</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Strawberry)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (62%) · Matching: form/spec, pack size · Not matching: brand, product name · Different brand and product name</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="12" ht="64" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Benzo-Jel Topical Anesthetic Strawberry 1oz/Jr
+SKU: 5700360  ·  Schein price: $6.29/unit</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>iSmile Topical Anesthetic Gel w/ 20% Benzocaine Strawberry (1oz)</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>iSmile Dental Products</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>https://www.ismiledentalproducts.com/anesthetics/topical-anesthetics/ismile-topical-anesthetic-gel-w-3-20-6-benzocaine-10--0105</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (62%)</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Strawberry)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (62%) · Matching: form/spec, pack size · Not matching: brand, product name · Different brand and product name</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="13" ht="64" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Benzo-Jel Topical Anesthetic Strawberry 1oz/Jr
+SKU: 5700360  ·  Schein price: $6.29/unit</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>House Brand Strawberry flavored Topical Anesthetic Gel (Benzocaine 20%)</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Net32</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/house-brand-strawberry-flavored-topical-anesthetic-gel-d-78066</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>POSSIBLE (62%)</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Strawberry)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (62%) · Matching: form/spec, pack size · Not matching: brand, product name · Different brand and product name</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>Equiv $8.68 &gt; Schein $6.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="64" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Maxima HP Mixing Tips Yellow 4.2mm 48/Bg
+SKU: 1126863  ·  Schein price: $34.29/unit</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Mixing Tips, Green, 6.5mm, High Performance, Bag of 48.</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Pricenex</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>https://pricenex.com/mixing-tips-green-6-5mm-high-performance-bag-of-48/</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (51%)</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Yellow 4.2mm)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (51%) · Matching: pack size · Not matching: brand, product name, form/spec · Different product variant and size</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="n">
+        <v>28.34</v>
+      </c>
+    </row>
+    <row r="15" ht="64" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Maxima HP Mixing Tips Yellow 4.2mm 48/Bg
+SKU: 1126863  ·  Schein price: $34.29/unit</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>MARK3 High Performance Mixing Tips 4.2 mm, YELLOW, Package of 50 tips - #1412</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>US Dental Depot</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>https://usdentaldepot.com/mark3-high-performance-mixing-tips-mark3-1412</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (47%)</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page 50 vs ordered 48) · VARIANT MISMATCH (ordered: Yellow 4.2mm)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (47%) · Matching: form/spec · Not matching: brand, product name, pack size · Different brand, product name, and pack quantity</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>15.17</v>
+      </c>
+    </row>
+    <row r="16" ht="64" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Maxima HP Mixing Tips Yellow 4.2mm 48/Bg
+SKU: 1126863  ·  Schein price: $34.29/unit</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Hexa T-Mixer Yellow Mixing Tips, Small 4.2mm, 48/Pk. 1:1 &amp; 2:1 Ratio</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Net32</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>23.86</v>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/hexa-tmixer-yellow-mixing-tips-small-42mm-d-160216</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (62%)</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Yellow 4.2mm)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (62%) · Matching: form/spec, pack size · Not matching: brand, product name · Different brand and product name</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="n">
+        <v>10.43</v>
+      </c>
+    </row>
+    <row r="17" ht="64" customHeight="1">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Maxima HP Mixing Tips Yellow 4.2mm 48/Bg
+SKU: 1126863  ·  Schein price: $34.29/unit</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Dental City Mixing Tips HP Yellow 4.2mm 48/Bag</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>Dental City</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>40.13</v>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>https://www.dentalcity.com/product/15798/dental-city-mixing-tips-hp-yellow-42mm-48bag</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>POSSIBLE (62%)</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Yellow 4.2mm)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (62%) · Matching: form/spec, pack size · Not matching: brand, product name · Different brand and product name</t>
+        </is>
+      </c>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>Equiv $40.13 &gt; Schein $34.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="64" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Maxima HP Mixing Tips Yellow 4.2mm 48/Bg
+SKU: 1126863  ·  Schein price: $34.29/unit</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>Ultrasonic Cleaning Tablets 64/Pk</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Frontier Dental Supply</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>42.99</v>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>https://frontierdental.com/us/en/product/hp-mixing-tips-42-mm-yellow-48pk-100623-160524</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>POSSIBLE (39%)</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page 64 vs ordered 48) · VARIANT MISMATCH (ordered: Yellow 4.2mm)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (39%) · Matching: form/spec · Not matching: brand, product name, pack size · Different product name and pack quantity, scraped product name does not match title</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>Equiv $42.99 &gt; Schein $34.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="64" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Acclean Prophy Angle Soft Short Gray 500/Bx
+SKU: 5703169  ·  Schein price: $222.77/unit</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Snap-On Disposable Contra Prophy Angles</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>The Dentists Supply Company</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>71.86</v>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Preventives/Prophy-Products/Prophy-Angles/c/445/manufacturer/ACCLEAN%20by%20Henry%20Schein</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (62%)</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page 100 vs ordered 500) · VARIANT MISMATCH (ordered: Soft Short Gray)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (62%) · Matching: brand, form/spec · Not matching: product name, pack size · Different product name and pack quantity</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>150.91</v>
+      </c>
+    </row>
+    <row r="20" ht="64" customHeight="1">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Acclean Prophy Angle Soft Short Gray 500/Bx
+SKU: 5703169  ·  Schein price: $222.77/unit</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Core Elite Flex Disposable Prophy Angle 500/Pk</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Crazy Dental Price Club</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>263.85</v>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>https://www.crazydentalprices.com/Core-Elite-Flex-Disposable-Prophy-Angle-500-Pk</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>POSSIBLE (68%)</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Soft Short Gray)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (68%) · Matching: form/spec, pack size · Not matching: brand, product name · Different brand and product name</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="inlineStr">
+        <is>
+          <t>Equiv $263.85 &gt; Schein $222.77</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="64" customHeight="1">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>Acclean Prophy Angle Soft Short Gray 500/Bx
+SKU: 5703169  ·  Schein price: $222.77/unit</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>Denticator - Disposable Prophy Angles 500/Pack</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Dental City</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>355.09</v>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>https://dentalcity.com/product/13289/denticator-disposable-prophy-angles-500pack</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>POSSIBLE (66%)</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Soft Short Gray)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (66%) · Matching: form/spec, pack size · Not matching: brand, product name · Different brand and variant</t>
+        </is>
+      </c>
+      <c r="H21" s="18" t="inlineStr">
+        <is>
+          <t>Equiv $355.09 &gt; Schein $222.77</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="64" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx
+SKU: 2906663  ·  Schein price: $82.19/unit</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Dental Mixing Tips for Crown and Bridge Material (1:1 ratio, Blue / White) - 25 pcs</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>UC Dental Products</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>http://www.ucdpi.com/impression-materials/mixing-tips.htm</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (66%)</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Fine)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (66%) · Matching: form/spec, pack size · Not matching: brand, product name · Different product name and brand</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="n">
+        <v>70.23999999999999</v>
+      </c>
+    </row>
+    <row r="23" ht="64" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx
+SKU: 2906663  ·  Schein price: $82.19/unit</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Luxatemp Automix Plus Fine Mixing Cannulas</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Pearson Dental Supply</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>https://www.pearsondental.com/catalog/product.asp?majcatid=13577&amp;catid=7775&amp;subcatid=22416&amp;pid=73558&amp;page=1</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (62%)</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page 1 vs ordered 25) · VARIANT MISMATCH (ordered: Fine)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (62%) · Matching: brand, form/spec · Not matching: product name, pack size · Different variant and pack quantity</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="n">
+        <v>13.39</v>
+      </c>
+    </row>
+    <row r="24" ht="64" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Denture Boxes Assorted Assorted 12/Pk
+SKU: 5703375  ·  Schein price: $29.46/unit</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Denture Box - 12 Pack</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Zirc Dental Products</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>https://zirc.com/products/denture-box</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>LOGIN-GATED price
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · login required for pricing (public pricing only)</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="n">
+        <v>12.96</v>
+      </c>
+    </row>
+    <row r="25" ht="64" customHeight="1">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>Denture Boxes Assorted Assorted 12/Pk
+SKU: 5703375  ·  Schein price: $29.46/unit</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>Denture Storage Boxes</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>Keystone Industries</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="n">
+        <v>140.45</v>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>https://dental.keystoneindustries.com/product/denture-storage-boxes/</t>
+        </is>
+      </c>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page 120 vs ordered 12) · VARIANT MISMATCH (ordered: Assorted)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · price 140.45 failed sanity vs Schein unit 29.46</t>
+        </is>
+      </c>
+      <c r="H25" s="18" t="inlineStr">
+        <is>
+          <t>Equiv $140.45 &gt; Schein $29.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="64" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Barrier Film Blue 4"X6" 1200/Bx
+SKU: 1469109  ·  Schein price: $24.31/unit</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>JMU Dental Barrier Film 4" x 6" Self Adhesive Wrap 1200 Sheets/Roll</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>JMU Dental</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>https://www.jmudental.com/products/jmu-dental-barrier-film</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (77%)</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Blue)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (77%) · Matching: brand, form/spec, pack size · Not matching: product name · Different variant (Clear vs Blue)</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="n">
+        <v>17.32</v>
+      </c>
+    </row>
+    <row r="27" ht="64" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea
+SKU: 1459489  ·  Schein price: $120.37/unit</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>ClearView™ Large Adult Nasal Masks 12/Pack</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Practicon, Inc.</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>98.98999999999999</v>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>https://www.practicon.com/clearview-large-adult-nasal-masks-12-pack/p/704434</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (68%)</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Medium)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (68%) · Matching: form/spec, pack size · Not matching: brand, product name · Different brand and product name</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>21.38</v>
+      </c>
+    </row>
+    <row r="28" ht="64" customHeight="1">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea
+SKU: 1459489  ·  Schein price: $120.37/unit</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>Silhouette Low Profile Nasal Masks Medium 12/Pack</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>Supply Clinic</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>140.08</v>
+      </c>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>https://www.supplyclinic.com/items/silhouette-low-profile-nasal-masks-medium-12-pack-porter-instrument-division-sil-med-12</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>LOGIN-GATED price
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · login required for pricing (public pricing only)</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>Equiv $140.08 &gt; Schein $120.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="64" customHeight="1">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>SILHOUETTE MEDIUM, 12 PK Ea
+SKU: 1459489  ·  Schein price: $120.37/unit</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>Axess Nasal Mask, Medium, Unscented, 24/bx</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>Net32</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="n">
+        <v>161.2</v>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/axess-nasal-mask-medium-unscented-24-low-d-148821</t>
+        </is>
+      </c>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>POSSIBLE (51%)</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page 24 vs ordered 12) · VARIANT MISMATCH (ordered: Medium)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (51%) · Matching: form/spec · Not matching: brand, product name, pack size · Different brand and product name</t>
+        </is>
+      </c>
+      <c r="H29" s="18" t="inlineStr">
+        <is>
+          <t>Equiv $161.20 &gt; Schein $120.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx
+SKU: 5701400  ·  Schein price: $17.61/unit</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>Exel Luer Lock Sterile 3cc Syringe with Needle, BX of 100</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Medical and Lab Supplies</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>20.95</v>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>https://www.medical-and-lab-supplies.com/products/exel-luer-lock-sterile-3cc-syringe-with-needle-bx-of-100-click-for-all-available-sizes</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>POSSIBLE (77%)</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Non-Sterile)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (77%) · Matching: brand, form/spec, pack size · Not matching: product name · Different variant (sterile vs non-sterile) and disagreement between title and scraped product name.</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>Equiv $20.95 &gt; Schein $17.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>Luer-Lock Syringes 3cc Non-Ster 100/Bx
+SKU: 5701400  ·  Schein price: $17.61/unit</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Syringes with Needle, Luer-lock Tip, 3cc</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>Bound Tree Medical</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>https://www.boundtree.com/iv-drug-delivery/syringes-needles/syringes-with-needle-luer-lock-tip-3cc/p/group002614</t>
+        </is>
+      </c>
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t>LOGIN-GATED price
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · login required for pricing (public pricing only)</t>
+        </is>
+      </c>
+      <c r="H31" s="18" t="inlineStr">
+        <is>
+          <t>Equiv $30.00 &gt; Schein $17.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea
+SKU: 7770371  ·  Schein price: $32.20/unit</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Amtouch</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>https://www.amtouch.com/shop-by-category/preventives/3m-clinpro-sealant/</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (70%)</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page 1 vs ordered ?) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (70%) · Matching: brand, product name · Not matching: form/spec, pack size · different product size and packaging</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="n">
+        <v>23.98</v>
+      </c>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea
+SKU: 7770371  ·  Schein price: $32.20/unit</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>3M™ Clinpro™ Sealant</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>Top Quality Manufacturing, LLC</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>https://topqualitygloves.com/products/3m-clinpro-sealant</t>
+        </is>
+      </c>
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t>LOGIN-GATED price
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · login required for pricing (public pricing only)</t>
+        </is>
+      </c>
+      <c r="H33" s="18" t="inlineStr">
+        <is>
+          <t>Equiv $33.25 &gt; Schein $32.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea
+SKU: 7770371  ·  Schein price: $32.20/unit</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>Prevent Seal Self-Etching Sealant 1.2ml</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>Supply Clinic</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="n">
+        <v>40.39</v>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>https://www.supplyclinic.com/items/prevent-seal-self-etching-sealant-1-2ml-itena-usa-pvseal-1-2</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>POSSIBLE (70%)</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: specified)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (70%) · Matching: form/spec, pack size · Not matching: brand, product name · different product, not Clinpro Sealant</t>
+        </is>
+      </c>
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>Equiv $40.39 &gt; Schein $32.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea
+SKU: 7770371  ·  Schein price: $32.20/unit</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>3M Clinpro Sealant Introductory Kit</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>Supply Clinic</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="n">
+        <v>89.81</v>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>https://www.supplyclinic.com/items/3m-clinpro-sealant-introductory-kit-12626-1-2-ml-syringe-2-syringes-kit-3m-12626</t>
+        </is>
+      </c>
+      <c r="F35" s="18" t="inlineStr">
+        <is>
+          <t>POSSIBLE (70%)</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page 1 vs ordered ?) · VARIANT MISMATCH (ordered: specified)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (70%) · Matching: brand, form/spec · Not matching: product name, pack size · different product, Introductory Kit</t>
+        </is>
+      </c>
+      <c r="H35" s="18" t="inlineStr">
+        <is>
+          <t>Equiv $89.81 &gt; Schein $32.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Purevac SC Evacuation Cleaner 5 Liter Ea
+SKU: 3120099  ·  Schein price: $144.39/unit</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>PureVac SC Evacuation System Cleaner (Sultan)</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>skydentalsupply.com</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>https://www.skydentalsupply.com/purevac-sc-evac-cleaner-.htm</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>LOGIN-GATED price
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · login required for pricing (public pricing only)</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="n">
+        <v>119.4</v>
+      </c>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Purevac SC Evacuation Cleaner 5 Liter Ea
+SKU: 3120099  ·  Schein price: $144.39/unit</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Purevac SC Evacuation Cleaner 2 Liter</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Scott's Dental Supply</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>https://www.scottsdental.com/purevac-sc.html</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · volume/size mismatch after normalization</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="n">
+        <v>67.44</v>
+      </c>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>Benzo-Jel Topical Anesthetic Strawberry 1oz/Jr
+SKU: 5700360  ·  Schein price: $6.29/unit</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>Benzo-Jel Topical Anesthetic Gel</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>The Dentists Supply Company</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Pharmaceutical-Products/Topical-Anesthetics/Benzo-Jel-Topical-Anesthetic-Gel/p/300231-1</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>POSSIBLE — unverified listing, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>Equiv $6.50 &gt; Schein $6.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>Benzo-Jel Topical Anesthetic Strawberry 1oz/Jr
+SKU: 5700360  ·  Schein price: $6.29/unit</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>ProJel-20, Cherry Flavor, 60 gm Jar. 20% Benzocaine ...</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>Net32</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/projel20-cherry-flavor-60-gm-jar-20-d-101965</t>
+        </is>
+      </c>
+      <c r="F39" s="18" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G39" s="17" t="inlineStr">
+        <is>
+          <t>POSSIBLE — unverified listing, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+      <c r="H39" s="18" t="inlineStr">
+        <is>
+          <t>Equiv $7.00 &gt; Schein $6.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>Benzo-Jel Topical Anesthetic Strawberry 1oz/Jr
+SKU: 5700360  ·  Schein price: $6.29/unit</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>Benzo-Jel Topical Anesthetic, Strawberry, 1oz 00404003330</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>zoro.com</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>https://www.zoro.com/benzo-jel-topical-anesthetic-strawberry-1oz-00404003330/i/G622895661/</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G40" s="13" t="inlineStr">
+        <is>
+          <t>POSSIBLE — unverified listing, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>Equiv $11.59 &gt; Schein $6.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="64" customHeight="1">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>Maxima HP Mixing Tips Yellow 4.2mm 48/Bg
+SKU: 1126863  ·  Schein price: $34.29/unit</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>MARK3 High Performance Mixing Tips 4.2 mm, Yellow ...</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>Net32</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="n">
+        <v>234</v>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/mark3-high-performance-mixing-tips-42-mm-d-157605</t>
+        </is>
+      </c>
+      <c r="F41" s="18" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="inlineStr">
+        <is>
+          <t>POSSIBLE — unverified listing, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+      <c r="H41" s="18" t="inlineStr">
+        <is>
+          <t>Equiv $234.00 &gt; Schein $34.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="64" customHeight="1">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>Acclean Prophy Angle Soft Short Gray 500/Bx
+SKU: 5703169  ·  Schein price: $222.77/unit</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>Prophy Angles</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>Practicon, Inc.</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="n">
+        <v>236.99</v>
+      </c>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>https://www.practicon.com/exam-hygiene/prophylaxis/prophy-angles/</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>POSSIBLE — unverified listing, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+      <c r="H42" s="14" t="inlineStr">
+        <is>
+          <t>Equiv $236.99 &gt; Schein $222.77</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="64" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx
+SKU: 2906663  ·  Schein price: $82.19/unit</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx | 110351</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>Supply Clinic</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>69.48999999999999</v>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>https://www.supplyclinic.com/items/luxatemp-plus-mixing-tips-fine-25-bx-dmg-america-110351</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>POSSIBLE — unverified listing, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="44" ht="64" customHeight="1">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx
+SKU: 2906663  ·  Schein price: $82.19/unit</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>Luxatemp Automix Plus Fine Mixing Tips, Box of 25</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>The Dental Market U.S.</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="n">
+        <v>80.95</v>
+      </c>
+      <c r="E44" s="16" t="inlineStr">
+        <is>
+          <t>https://thedentalmarket.net/featured-items/luxatemp-automix-plus-fine-mixing-tips-box-of-25/</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t>POSSIBLE — unverified listing, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+      <c r="H44" s="15" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="45" ht="64" customHeight="1">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>Luxatemp Plus Mixing Tips Fine 25/Bx
+SKU: 2906663  ·  Schein price: $82.19/unit</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>Luxatemp Plus</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>Scott's Dental Supply</t>
+        </is>
+      </c>
+      <c r="D45" s="19" t="n">
+        <v>449.95</v>
+      </c>
+      <c r="E45" s="20" t="inlineStr">
+        <is>
+          <t>https://www.scottsdental.com/luxatemp-plus.html</t>
+        </is>
+      </c>
+      <c r="F45" s="18" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="inlineStr">
+        <is>
+          <t>POSSIBLE — unverified listing, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+      <c r="H45" s="18" t="inlineStr">
+        <is>
+          <t>Equiv $449.95 &gt; Schein $82.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="64" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>Barrier Film Blue 4"X6" 1200/Bx
+SKU: 1469109  ·  Schein price: $24.31/unit</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>4"x 6" Unipack Barrier Film - Blue | 1200 Perforated Sheets</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>Cam Supply</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>https://www.camsupply.com/products/barrier-film-blue-1200-perforated-sheets</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>POSSIBLE — unverified listing, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="n">
+        <v>9.31</v>
+      </c>
+    </row>
+    <row r="47" ht="64" customHeight="1">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>Barrier Film Blue 4"X6" 1200/Bx
+SKU: 1469109  ·  Schein price: $24.31/unit</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>Dental Barrier Film 4" x 6" blue 1200 sheets single</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>Darkside Tattoo Supply Inc</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>https://www.darksidesupply.com/dental-barrier-film-4-x-6-blue-1200-sheets-single.html</t>
+        </is>
+      </c>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>POSSIBLE — unverified listing, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+      <c r="H47" s="11" t="n">
+        <v>9.06</v>
+      </c>
+    </row>
+    <row r="48" ht="64" customHeight="1">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>Barrier Film Blue 4"X6" 1200/Bx
+SKU: 1469109  ·  Schein price: $24.31/unit</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>3D Essentials Barrier Film Blue 4X6 1200/Roll | BARB</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>Supply Clinic</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="E48" s="16" t="inlineStr">
+        <is>
+          <t>https://www.supplyclinic.com/items/3d-essentials-barrier-film-blue-4x6-1200-roll-3d-dental-barb</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>POSSIBLE — unverified listing, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+      <c r="H48" s="14" t="inlineStr">
+        <is>
+          <t>Equiv $100.00 &gt; Schein $24.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="64" customHeight="1">
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t>Barrier Film Blue 4"X6" 1200/Bx
+SKU: 1469109  ·  Schein price: $24.31/unit</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>Primo 4" x 6" Barrier Film, Blue. Roll of 1200 Sheets. Non- ...</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>Net32</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="n">
+        <v>189</v>
+      </c>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/primo-4-x-6-barrier-film-blue-d-162058</t>
+        </is>
+      </c>
+      <c r="F49" s="18" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="inlineStr">
+        <is>
+          <t>POSSIBLE — unverified listing, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+      <c r="H49" s="18" t="inlineStr">
+        <is>
+          <t>Equiv $189.00 &gt; Schein $24.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="64" customHeight="1">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>Barrier Film Blue 4"X6" 1200/Bx
+SKU: 1469109  ·  Schein price: $24.31/unit</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>Dukal Barrier Film, Blue, 4" x 6" Sheet, 1200 sheets/Roll ...</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>Global Industrial</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="n">
+        <v>239.95</v>
+      </c>
+      <c r="E50" s="16" t="inlineStr">
+        <is>
+          <t>https://www.globalindustrial.com/p/barrier-film-blue-4-x-6-sheet-1200-sheets-roll-12-rolls-case</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t>POSSIBLE — unverified listing, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>Equiv $239.95 &gt; Schein $24.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="64" customHeight="1">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea
+SKU: 7770371  ·  Schein price: $32.20/unit</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>3M™ Clinpro™ Sealant Refill 1.2ml Syringe</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>Benco Dental</t>
+        </is>
+      </c>
+      <c r="D51" s="19" t="n">
+        <v>43.49</v>
+      </c>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>https://shop.benco.com/Product/3168-583/3m-clinpro-sealant-refill-12ml-syringe</t>
+        </is>
+      </c>
+      <c r="F51" s="18" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G51" s="17" t="inlineStr">
+        <is>
+          <t>POSSIBLE — unverified listing, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+      <c r="H51" s="18" t="inlineStr">
+        <is>
+          <t>Equiv $43.49 &gt; Schein $32.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="64" customHeight="1">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>Clinpro Sealant Reﬁll Syringe 1.2mL Pkg Ea
+SKU: 7770371  ·  Schein price: $32.20/unit</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>iris® Pit and Fissure Sealant A2 1.2ml Syringe Pack of 4</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>Benco Dental</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="n">
+        <v>77.98999999999999</v>
+      </c>
+      <c r="E52" s="16" t="inlineStr">
+        <is>
+          <t>https://shop.benco.com/Product/4006-862/iris-pit-and-fissure-sealant-a2-12ml-syringe-pack-</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G52" s="13" t="inlineStr">
+        <is>
+          <t>POSSIBLE — unverified listing, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · not scraped — enough verified candidates found</t>
+        </is>
+      </c>
+      <c r="H52" s="14" t="inlineStr">
+        <is>
+          <t>Equiv $77.99 &gt; Schein $32.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="64" customHeight="1">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>Oral-B Glide Floss Reﬁll Unﬂ 160 Meter 2/Bx
+SKU: 3250497  ·  Schein price: $16.62/unit</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>— no public candidate found this run —</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D53" s="18" t="n"/>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?tbm=shop&amp;q=Oral-B+Glide+Floss+Unflavored+160+Meter+2+pack</t>
+        </is>
+      </c>
+      <c r="F53" s="18" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G53" s="17" t="inlineStr">
+        <is>
+          <t>POSSIBLE — no usable public listing found; link opens a supplier search</t>
+        </is>
+      </c>
+      <c r="H53" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="64" customHeight="1">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk
+SKU: 7772551  ·  Schein price: $278.99/unit</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>— no public candidate found this run —</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="n"/>
+      <c r="E54" s="16" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?tbm=shop&amp;q=3M+Clinpro+Clear+Fluoride+Treatment+No+Flavor+100+pack</t>
+        </is>
+      </c>
+      <c r="F54" s="14" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G54" s="13" t="inlineStr">
+        <is>
+          <t>POSSIBLE — no usable public listing found; link opens a supplier search</t>
+        </is>
+      </c>
+      <c r="H54" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId51"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>